--- a/outputs/submission/q4_base_location.xlsx
+++ b/outputs/submission/q4_base_location.xlsx
@@ -9,13 +9,14 @@
   <sheets>
     <sheet name="base_results" sheetId="1" r:id="rId1"/>
     <sheet name="assignment" sheetId="2" r:id="rId2"/>
+    <sheet name="feasibility_notes" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="90">
   <si>
     <t>scenario</t>
   </si>
@@ -273,6 +274,18 @@
   </si>
   <si>
     <t>Windsor Terrace</t>
+  </si>
+  <si>
+    <t>base_zone_id</t>
+  </si>
+  <si>
+    <t>base_zone_name</t>
+  </si>
+  <si>
+    <t>feasibility_note</t>
+  </si>
+  <si>
+    <t>TLC zone-level base; choose a legal parking/dispatch facility inside the zone. Avoid interpreting the zone label as the exact depot parcel.</t>
   </si>
 </sst>
 </file>
@@ -661,10 +674,10 @@
         <v>13</v>
       </c>
       <c r="D2">
-        <v>25558.48077272759</v>
+        <v>26382.41844106002</v>
       </c>
       <c r="E2">
-        <v>0.3245667292688224</v>
+        <v>0.3231573857944056</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -678,7 +691,7 @@
         <v>14</v>
       </c>
       <c r="D3">
-        <v>37840.12704180198</v>
+        <v>38978.6604556879</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -695,10 +708,10 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>47129.62007704948</v>
+        <v>49031.48608640542</v>
       </c>
       <c r="E4">
-        <v>-0.2454931777841391</v>
+        <v>-0.2579058775543577</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -712,10 +725,10 @@
         <v>16</v>
       </c>
       <c r="D5">
-        <v>30563.35873867787</v>
+        <v>31673.91313175506</v>
       </c>
       <c r="E5">
-        <v>0.1923029564643233</v>
+        <v>0.1874037547349041</v>
       </c>
     </row>
   </sheetData>
@@ -762,13 +775,13 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>0.7861391375372468</v>
+        <v>0.745565033370428</v>
       </c>
       <c r="D2">
-        <v>5.80866537068958</v>
+        <v>5.849361022863494</v>
       </c>
       <c r="E2">
-        <v>4.566419184756379</v>
+        <v>4.361079046206902</v>
       </c>
       <c r="F2">
         <v>111</v>
@@ -788,13 +801,13 @@
         <v>26</v>
       </c>
       <c r="C3">
-        <v>7.322297995673891</v>
+        <v>7.341706281548541</v>
       </c>
       <c r="D3">
-        <v>5.80866537068958</v>
+        <v>5.849361022863494</v>
       </c>
       <c r="E3">
-        <v>42.53277880134065</v>
+        <v>42.94429056460211</v>
       </c>
       <c r="F3">
         <v>111</v>
@@ -814,13 +827,13 @@
         <v>27</v>
       </c>
       <c r="C4">
-        <v>11.62018561329523</v>
+        <v>12.20216708574654</v>
       </c>
       <c r="D4">
-        <v>5.754416666666667</v>
+        <v>5.601083333333334</v>
       </c>
       <c r="E4">
-        <v>66.86738976290631</v>
+        <v>68.34535469452352</v>
       </c>
       <c r="F4">
         <v>111</v>
@@ -840,13 +853,13 @@
         <v>28</v>
       </c>
       <c r="C5">
-        <v>2.799648386947021</v>
+        <v>2.822701005736524</v>
       </c>
       <c r="D5">
-        <v>2.983000000000001</v>
+        <v>2.993000000000001</v>
       </c>
       <c r="E5">
-        <v>8.351351138262967</v>
+        <v>8.448344110169421</v>
       </c>
       <c r="F5">
         <v>111</v>
@@ -866,13 +879,13 @@
         <v>29</v>
       </c>
       <c r="C6">
-        <v>6.111878476579959</v>
+        <v>6.465768028453207</v>
       </c>
       <c r="D6">
-        <v>3.469250000000001</v>
+        <v>3.47925</v>
       </c>
       <c r="E6">
-        <v>21.20363440487503</v>
+        <v>22.49602341299582</v>
       </c>
       <c r="F6">
         <v>111</v>
@@ -892,13 +905,13 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>24.88262106655043</v>
+        <v>25.9600841186291</v>
       </c>
       <c r="D7">
-        <v>5.055333333333334</v>
+        <v>5.002000000000001</v>
       </c>
       <c r="E7">
-        <v>125.7899436984346</v>
+        <v>129.8523407613828</v>
       </c>
       <c r="F7">
         <v>65</v>
@@ -918,13 +931,13 @@
         <v>31</v>
       </c>
       <c r="C8">
-        <v>6.03180130520032</v>
+        <v>6.098383669369557</v>
       </c>
       <c r="D8">
-        <v>4.59975</v>
+        <v>4.639750000000001</v>
       </c>
       <c r="E8">
-        <v>27.74477805359517</v>
+        <v>28.29497562995741</v>
       </c>
       <c r="F8">
         <v>111</v>
@@ -944,13 +957,13 @@
         <v>32</v>
       </c>
       <c r="C9">
-        <v>4.464689909067117</v>
+        <v>4.618268197974807</v>
       </c>
       <c r="D9">
-        <v>2.163</v>
+        <v>2.213</v>
       </c>
       <c r="E9">
-        <v>9.657124273312172</v>
+        <v>10.22022752211825</v>
       </c>
       <c r="F9">
         <v>222</v>
@@ -970,13 +983,13 @@
         <v>33</v>
       </c>
       <c r="C10">
-        <v>37.44260923368128</v>
+        <v>38.50316475293453</v>
       </c>
       <c r="D10">
-        <v>14.96212500000001</v>
+        <v>15.32712500000001</v>
       </c>
       <c r="E10">
-        <v>560.2209996804937</v>
+        <v>590.1428190638219</v>
       </c>
       <c r="F10">
         <v>65</v>
@@ -996,13 +1009,13 @@
         <v>34</v>
       </c>
       <c r="C11">
-        <v>0.2537254417051208</v>
+        <v>0.240586001509577</v>
       </c>
       <c r="D11">
-        <v>5.80866537068958</v>
+        <v>5.849361022863494</v>
       </c>
       <c r="E11">
-        <v>1.473806186895453</v>
+        <v>1.407274379876698</v>
       </c>
       <c r="F11">
         <v>65</v>
@@ -1022,13 +1035,13 @@
         <v>35</v>
       </c>
       <c r="C12">
-        <v>5.739968902964273</v>
+        <v>5.792965279038185</v>
       </c>
       <c r="D12">
-        <v>2.571333333333334</v>
+        <v>2.404666666666667</v>
       </c>
       <c r="E12">
-        <v>14.7593733724888</v>
+        <v>13.93015050766049</v>
       </c>
       <c r="F12">
         <v>222</v>
@@ -1048,13 +1061,13 @@
         <v>36</v>
       </c>
       <c r="C13">
-        <v>2.73577192652567</v>
+        <v>2.557964414033694</v>
       </c>
       <c r="D13">
-        <v>4.054666666666667</v>
+        <v>4.128</v>
       </c>
       <c r="E13">
-        <v>11.09264323808608</v>
+        <v>10.55927710113109</v>
       </c>
       <c r="F13">
         <v>65</v>
@@ -1074,13 +1087,13 @@
         <v>37</v>
       </c>
       <c r="C14">
-        <v>4.521404831642053</v>
+        <v>4.539136458158642</v>
       </c>
       <c r="D14">
-        <v>6.142308899592942</v>
+        <v>6.206058899592942</v>
       </c>
       <c r="E14">
-        <v>27.77186513605752</v>
+        <v>28.17014821262222</v>
       </c>
       <c r="F14">
         <v>111</v>
@@ -1100,13 +1113,13 @@
         <v>38</v>
       </c>
       <c r="C15">
-        <v>7.009948831877653</v>
+        <v>7.028618253948109</v>
       </c>
       <c r="D15">
-        <v>3.94175</v>
+        <v>3.849250000000001</v>
       </c>
       <c r="E15">
-        <v>27.63146580805374</v>
+        <v>27.05490881400976</v>
       </c>
       <c r="F15">
         <v>222</v>
@@ -1126,13 +1139,13 @@
         <v>39</v>
       </c>
       <c r="C16">
-        <v>8.645191346491213</v>
+        <v>9.149581663248799</v>
       </c>
       <c r="D16">
-        <v>7.484125</v>
+        <v>7.459125000000001</v>
       </c>
       <c r="E16">
-        <v>64.70169268605855</v>
+        <v>68.24787332388071</v>
       </c>
       <c r="F16">
         <v>111</v>
@@ -1152,13 +1165,13 @@
         <v>40</v>
       </c>
       <c r="C17">
-        <v>7.954193931385616</v>
+        <v>7.975525574990453</v>
       </c>
       <c r="D17">
-        <v>7.030000000000001</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="E17">
-        <v>55.91798333764089</v>
+        <v>57.42378413993126</v>
       </c>
       <c r="F17">
         <v>65</v>
@@ -1178,13 +1191,13 @@
         <v>41</v>
       </c>
       <c r="C18">
-        <v>13.94925417228803</v>
+        <v>14.45065491706647</v>
       </c>
       <c r="D18">
-        <v>3.294</v>
+        <v>3.274000000000001</v>
       </c>
       <c r="E18">
-        <v>45.94884324351678</v>
+        <v>47.31144419847563</v>
       </c>
       <c r="F18">
         <v>65</v>
@@ -1204,13 +1217,13 @@
         <v>42</v>
       </c>
       <c r="C19">
-        <v>0.8685782852997461</v>
+        <v>0.8373578803924049</v>
       </c>
       <c r="D19">
-        <v>3.487710440003781</v>
+        <v>3.567710440003781</v>
       </c>
       <c r="E19">
-        <v>3.029349553600507</v>
+        <v>2.98745045189542</v>
       </c>
       <c r="F19">
         <v>65</v>
@@ -1230,13 +1243,13 @@
         <v>43</v>
       </c>
       <c r="C20">
-        <v>4.288708031910989</v>
+        <v>4.173798336670656</v>
       </c>
       <c r="D20">
-        <v>5.80866537068958</v>
+        <v>5.849361022863494</v>
       </c>
       <c r="E20">
-        <v>24.91166982995962</v>
+        <v>24.41405330781382</v>
       </c>
       <c r="F20">
         <v>222</v>
@@ -1256,13 +1269,13 @@
         <v>44</v>
       </c>
       <c r="C21">
-        <v>15.45759622151422</v>
+        <v>15.93391957515696</v>
       </c>
       <c r="D21">
-        <v>4.196464285714286</v>
+        <v>4.232178571428571</v>
       </c>
       <c r="E21">
-        <v>64.86725048657652</v>
+        <v>67.43519298484554</v>
       </c>
       <c r="F21">
         <v>111</v>
@@ -1282,13 +1295,13 @@
         <v>45</v>
       </c>
       <c r="C22">
-        <v>3.97514743887</v>
+        <v>3.897183612393216</v>
       </c>
       <c r="D22">
-        <v>4.961000000000002</v>
+        <v>4.891000000000002</v>
       </c>
       <c r="E22">
-        <v>19.72070644423408</v>
+        <v>19.06112504821523</v>
       </c>
       <c r="F22">
         <v>111</v>
@@ -1308,13 +1321,13 @@
         <v>46</v>
       </c>
       <c r="C23">
-        <v>1.994669731576661</v>
+        <v>1.983265885217715</v>
       </c>
       <c r="D23">
-        <v>6.708374999999999</v>
+        <v>6.973375</v>
       </c>
       <c r="E23">
-        <v>13.38099256056558</v>
+        <v>13.83005674233008</v>
       </c>
       <c r="F23">
         <v>222</v>
@@ -1334,13 +1347,13 @@
         <v>47</v>
       </c>
       <c r="C24">
-        <v>32.76761727819967</v>
+        <v>33.66430664474652</v>
       </c>
       <c r="D24">
-        <v>13.04822738512074</v>
+        <v>13.66222738512074</v>
       </c>
       <c r="E24">
-        <v>427.5593211145606</v>
+        <v>459.929412142958</v>
       </c>
       <c r="F24">
         <v>65</v>
@@ -1360,13 +1373,13 @@
         <v>48</v>
       </c>
       <c r="C25">
-        <v>11.82052560370878</v>
+        <v>12.52841222415983</v>
       </c>
       <c r="D25">
-        <v>3.2775</v>
+        <v>3.2675</v>
       </c>
       <c r="E25">
-        <v>38.74177266615554</v>
+        <v>40.93658694244223</v>
       </c>
       <c r="F25">
         <v>65</v>
@@ -1386,13 +1399,13 @@
         <v>49</v>
       </c>
       <c r="C26">
-        <v>1.478455497664508</v>
+        <v>1.468197958233695</v>
       </c>
       <c r="D26">
-        <v>2.661500000000001</v>
+        <v>2.731500000000001</v>
       </c>
       <c r="E26">
-        <v>3.934909307034089</v>
+        <v>4.010382722915339</v>
       </c>
       <c r="F26">
         <v>111</v>
@@ -1412,13 +1425,13 @@
         <v>50</v>
       </c>
       <c r="C27">
-        <v>5.353767491539864</v>
+        <v>5.363602807817085</v>
       </c>
       <c r="D27">
-        <v>6.577000000000005</v>
+        <v>6.527000000000005</v>
       </c>
       <c r="E27">
-        <v>35.21172879185772</v>
+        <v>35.00823552662214</v>
       </c>
       <c r="F27">
         <v>111</v>
@@ -1438,13 +1451,13 @@
         <v>51</v>
       </c>
       <c r="C28">
-        <v>5.375049907722471</v>
+        <v>5.711714589658509</v>
       </c>
       <c r="D28">
-        <v>2.6385</v>
+        <v>2.7185</v>
       </c>
       <c r="E28">
-        <v>14.18206918152574</v>
+        <v>15.52729611198666</v>
       </c>
       <c r="F28">
         <v>111</v>
@@ -1464,13 +1477,13 @@
         <v>52</v>
       </c>
       <c r="C29">
-        <v>12.91545612174226</v>
+        <v>13.47745784217993</v>
       </c>
       <c r="D29">
-        <v>7.1330625</v>
+        <v>7.3655625</v>
       </c>
       <c r="E29">
-        <v>92.12675573239513</v>
+        <v>99.2690580776914</v>
       </c>
       <c r="F29">
         <v>222</v>
@@ -1490,13 +1503,13 @@
         <v>53</v>
       </c>
       <c r="C30">
-        <v>2.615911845230452</v>
+        <v>2.59776127746782</v>
       </c>
       <c r="D30">
-        <v>5.80866537068958</v>
+        <v>5.849361022863494</v>
       </c>
       <c r="E30">
-        <v>15.1949565481668</v>
+        <v>15.19524356312435</v>
       </c>
       <c r="F30">
         <v>222</v>
@@ -1516,13 +1529,13 @@
         <v>54</v>
       </c>
       <c r="C31">
-        <v>3.079408534455307</v>
+        <v>3.008073829269156</v>
       </c>
       <c r="D31">
-        <v>5.132375000000001</v>
+        <v>5.095708333333334</v>
       </c>
       <c r="E31">
-        <v>15.80467937702506</v>
+        <v>15.32826687908875</v>
       </c>
       <c r="F31">
         <v>65</v>
@@ -1542,13 +1555,13 @@
         <v>55</v>
       </c>
       <c r="C32">
-        <v>5.810112964203543</v>
+        <v>6.042475914545943</v>
       </c>
       <c r="D32">
-        <v>5.80866537068958</v>
+        <v>5.849361022863494</v>
       </c>
       <c r="E32">
-        <v>33.7490019749637</v>
+        <v>35.34462309613648</v>
       </c>
       <c r="F32">
         <v>111</v>
@@ -1568,13 +1581,13 @@
         <v>56</v>
       </c>
       <c r="C33">
-        <v>8.205891985075061</v>
+        <v>8.273337985917321</v>
       </c>
       <c r="D33">
-        <v>3.788666666666667</v>
+        <v>3.748666666666667</v>
       </c>
       <c r="E33">
-        <v>31.08938943412105</v>
+        <v>31.0139863298754</v>
       </c>
       <c r="F33">
         <v>111</v>
@@ -1594,13 +1607,13 @@
         <v>57</v>
       </c>
       <c r="C34">
-        <v>6.169885853583731</v>
+        <v>6.206073151157904</v>
       </c>
       <c r="D34">
-        <v>5.3245</v>
+        <v>5.3995</v>
       </c>
       <c r="E34">
-        <v>32.85155722740657</v>
+        <v>33.5096919796771</v>
       </c>
       <c r="F34">
         <v>111</v>
@@ -1620,13 +1633,13 @@
         <v>58</v>
       </c>
       <c r="C35">
-        <v>28.49746097978402</v>
+        <v>29.83121606480299</v>
       </c>
       <c r="D35">
-        <v>4.272000000000001</v>
+        <v>4.262</v>
       </c>
       <c r="E35">
-        <v>121.7411533056374</v>
+        <v>127.1406428681903</v>
       </c>
       <c r="F35">
         <v>65</v>
@@ -1646,13 +1659,13 @@
         <v>59</v>
       </c>
       <c r="C36">
-        <v>2.681151403454418</v>
+        <v>2.622867715503946</v>
       </c>
       <c r="D36">
-        <v>4.113999999999999</v>
+        <v>4.154</v>
       </c>
       <c r="E36">
-        <v>11.03025687381147</v>
+        <v>10.89539249020339</v>
       </c>
       <c r="F36">
         <v>111</v>
@@ -1672,13 +1685,13 @@
         <v>60</v>
       </c>
       <c r="C37">
-        <v>3.379638607354134</v>
+        <v>3.441056130829438</v>
       </c>
       <c r="D37">
-        <v>5.80866537068958</v>
+        <v>5.849361022863494</v>
       </c>
       <c r="E37">
-        <v>19.63118974398351</v>
+        <v>20.12797960915918</v>
       </c>
       <c r="F37">
         <v>222</v>
@@ -1698,13 +1711,13 @@
         <v>61</v>
       </c>
       <c r="C38">
-        <v>0.0282952973987074</v>
+        <v>0.0274674365258816</v>
       </c>
       <c r="D38">
-        <v>2.956499999999999</v>
+        <v>2.886499999999999</v>
       </c>
       <c r="E38">
-        <v>0.0836550467592784</v>
+        <v>0.0792847555319572</v>
       </c>
       <c r="F38">
         <v>111</v>
@@ -1724,13 +1737,13 @@
         <v>62</v>
       </c>
       <c r="C39">
-        <v>3.786251342058054</v>
+        <v>3.825339677968438</v>
       </c>
       <c r="D39">
-        <v>6.436496553227734</v>
+        <v>6.376496553227734</v>
       </c>
       <c r="E39">
-        <v>24.37019371281055</v>
+        <v>24.39226527149104</v>
       </c>
       <c r="F39">
         <v>65</v>
@@ -1750,13 +1763,13 @@
         <v>63</v>
       </c>
       <c r="C40">
-        <v>3.582216156420516</v>
+        <v>3.572505789499097</v>
       </c>
       <c r="D40">
-        <v>4.6645</v>
+        <v>4.5845</v>
       </c>
       <c r="E40">
-        <v>16.7092472616235</v>
+        <v>16.37815279195861</v>
       </c>
       <c r="F40">
         <v>111</v>
@@ -1776,13 +1789,13 @@
         <v>64</v>
       </c>
       <c r="C41">
-        <v>2.750618823692184</v>
+        <v>2.767953938427828</v>
       </c>
       <c r="D41">
-        <v>5.80866537068958</v>
+        <v>5.849361022863494</v>
       </c>
       <c r="E41">
-        <v>15.9774243091477</v>
+        <v>16.19076188052124</v>
       </c>
       <c r="F41">
         <v>111</v>
@@ -1802,13 +1815,13 @@
         <v>65</v>
       </c>
       <c r="C42">
-        <v>3.296808397313321</v>
+        <v>3.368600458684325</v>
       </c>
       <c r="D42">
-        <v>12.09005834215038</v>
+        <v>11.91672500881705</v>
       </c>
       <c r="E42">
-        <v>39.85860586640934</v>
+        <v>40.14268533071607</v>
       </c>
       <c r="F42">
         <v>111</v>
@@ -1828,13 +1841,13 @@
         <v>66</v>
       </c>
       <c r="C43">
-        <v>1.516688636481844</v>
+        <v>1.417548789534279</v>
       </c>
       <c r="D43">
-        <v>3.294000000000001</v>
+        <v>3.544000000000001</v>
       </c>
       <c r="E43">
-        <v>4.995972368571195</v>
+        <v>5.023792910109487</v>
       </c>
       <c r="F43">
         <v>222</v>
@@ -1854,13 +1867,13 @@
         <v>67</v>
       </c>
       <c r="C44">
-        <v>0.1954610306881022</v>
+        <v>0.197328374047944</v>
       </c>
       <c r="D44">
-        <v>5.80866537068958</v>
+        <v>5.849361022863494</v>
       </c>
       <c r="E44">
-        <v>1.135367720277273</v>
+        <v>1.154244899861072</v>
       </c>
       <c r="F44">
         <v>222</v>
@@ -1880,13 +1893,13 @@
         <v>68</v>
       </c>
       <c r="C45">
-        <v>3.313539259191428</v>
+        <v>3.154745087805411</v>
       </c>
       <c r="D45">
-        <v>3.723500000000002</v>
+        <v>3.693500000000002</v>
       </c>
       <c r="E45">
-        <v>12.33796343159929</v>
+        <v>11.65205098180929</v>
       </c>
       <c r="F45">
         <v>222</v>
@@ -1906,13 +1919,13 @@
         <v>69</v>
       </c>
       <c r="C46">
-        <v>6.700600198584287</v>
+        <v>6.752419312739973</v>
       </c>
       <c r="D46">
-        <v>5.2845</v>
+        <v>5.3345</v>
       </c>
       <c r="E46">
-        <v>35.40932174941867</v>
+        <v>36.02078082381139</v>
       </c>
       <c r="F46">
         <v>111</v>
@@ -1932,13 +1945,13 @@
         <v>70</v>
       </c>
       <c r="C47">
-        <v>3.61777963433221</v>
+        <v>3.594886018975857</v>
       </c>
       <c r="D47">
-        <v>7.228875</v>
+        <v>7.288875000000001</v>
       </c>
       <c r="E47">
-        <v>26.15247675413326</v>
+        <v>26.20267483156265</v>
       </c>
       <c r="F47">
         <v>222</v>
@@ -1958,13 +1971,13 @@
         <v>71</v>
       </c>
       <c r="C48">
-        <v>2.120760123483058</v>
+        <v>2.12592852023809</v>
       </c>
       <c r="D48">
-        <v>5.80866537068958</v>
+        <v>5.849361022863494</v>
       </c>
       <c r="E48">
-        <v>12.3187858888154</v>
+        <v>12.43532342367455</v>
       </c>
       <c r="F48">
         <v>111</v>
@@ -1984,13 +1997,13 @@
         <v>72</v>
       </c>
       <c r="C49">
-        <v>23.40172630842621</v>
+        <v>25.66391557713383</v>
       </c>
       <c r="D49">
-        <v>3.898277777777778</v>
+        <v>3.879388888888889</v>
       </c>
       <c r="E49">
-        <v>91.22642962977548</v>
+        <v>99.56030893531546</v>
       </c>
       <c r="F49">
         <v>111</v>
@@ -2010,13 +2023,13 @@
         <v>73</v>
       </c>
       <c r="C50">
-        <v>9.526158228192203</v>
+        <v>10.06765522243298</v>
       </c>
       <c r="D50">
-        <v>5.601083333333334</v>
+        <v>5.607749999999999</v>
       </c>
       <c r="E50">
-        <v>53.35680608262356</v>
+        <v>56.45689357359851</v>
       </c>
       <c r="F50">
         <v>111</v>
@@ -2036,13 +2049,13 @@
         <v>74</v>
       </c>
       <c r="C51">
-        <v>5.616671685113239</v>
+        <v>6.092554171704538</v>
       </c>
       <c r="D51">
-        <v>3.640000000000001</v>
+        <v>3.65</v>
       </c>
       <c r="E51">
-        <v>20.4446849338122</v>
+        <v>22.23782272672156</v>
       </c>
       <c r="F51">
         <v>111</v>
@@ -2062,13 +2075,13 @@
         <v>75</v>
       </c>
       <c r="C52">
-        <v>0.2567070836394975</v>
+        <v>0.2465956337974</v>
       </c>
       <c r="D52">
-        <v>5.80866537068958</v>
+        <v>5.849361022863494</v>
       </c>
       <c r="E52">
-        <v>1.491125547147463</v>
+        <v>1.442426888742831</v>
       </c>
       <c r="F52">
         <v>111</v>
@@ -2088,13 +2101,13 @@
         <v>76</v>
       </c>
       <c r="C53">
-        <v>2.372851367464393</v>
+        <v>2.4260424794793</v>
       </c>
       <c r="D53">
-        <v>3.5815</v>
+        <v>3.701500000000001</v>
       </c>
       <c r="E53">
-        <v>8.498367172573722</v>
+        <v>8.979996237792632</v>
       </c>
       <c r="F53">
         <v>111</v>
@@ -2114,13 +2127,13 @@
         <v>77</v>
       </c>
       <c r="C54">
-        <v>5.479686822169914</v>
+        <v>5.58336643499782</v>
       </c>
       <c r="D54">
-        <v>2.787</v>
+        <v>2.736999999999999</v>
       </c>
       <c r="E54">
-        <v>15.27188717338755</v>
+        <v>15.28167393258903</v>
       </c>
       <c r="F54">
         <v>222</v>
@@ -2140,13 +2153,13 @@
         <v>78</v>
       </c>
       <c r="C55">
-        <v>2.709147007317714</v>
+        <v>2.751724916137945</v>
       </c>
       <c r="D55">
-        <v>8.214499999999997</v>
+        <v>8.204499999999999</v>
       </c>
       <c r="E55">
-        <v>22.25428809161136</v>
+        <v>22.57652707445377</v>
       </c>
       <c r="F55">
         <v>65</v>
@@ -2166,13 +2179,13 @@
         <v>79</v>
       </c>
       <c r="C56">
-        <v>3.313518313947521</v>
+        <v>3.293675352324498</v>
       </c>
       <c r="D56">
-        <v>15.84678438081632</v>
+        <v>16.93678438081632</v>
       </c>
       <c r="E56">
-        <v>52.50861026301241</v>
+        <v>55.78426926272925</v>
       </c>
       <c r="F56">
         <v>222</v>
@@ -2192,13 +2205,13 @@
         <v>80</v>
       </c>
       <c r="C57">
-        <v>7.357317181874623</v>
+        <v>7.65442465999378</v>
       </c>
       <c r="D57">
-        <v>9.132999999999999</v>
+        <v>9.283000000000005</v>
       </c>
       <c r="E57">
-        <v>67.19437782206093</v>
+        <v>71.05602411872229</v>
       </c>
       <c r="F57">
         <v>111</v>
@@ -2218,13 +2231,13 @@
         <v>81</v>
       </c>
       <c r="C58">
-        <v>2.699824615211464</v>
+        <v>2.761465361488717</v>
       </c>
       <c r="D58">
-        <v>6.151624999999999</v>
+        <v>6.216625000000001</v>
       </c>
       <c r="E58">
-        <v>16.60830859855022</v>
+        <v>17.1669946028648</v>
       </c>
       <c r="F58">
         <v>111</v>
@@ -2244,13 +2257,13 @@
         <v>82</v>
       </c>
       <c r="C59">
-        <v>3.538973155073464</v>
+        <v>3.497788745797252</v>
       </c>
       <c r="D59">
-        <v>6.387499999999999</v>
+        <v>5.7875</v>
       </c>
       <c r="E59">
-        <v>22.60519102803175</v>
+        <v>20.2434523663016</v>
       </c>
       <c r="F59">
         <v>111</v>
@@ -2270,13 +2283,13 @@
         <v>83</v>
       </c>
       <c r="C60">
-        <v>3.779102849767777</v>
+        <v>3.744159174953809</v>
       </c>
       <c r="D60">
-        <v>8.342750000000001</v>
+        <v>8.229416666666669</v>
       </c>
       <c r="E60">
-        <v>31.52811029990012</v>
+        <v>30.8122459170178</v>
       </c>
       <c r="F60">
         <v>65</v>
@@ -2296,13 +2309,13 @@
         <v>84</v>
       </c>
       <c r="C61">
-        <v>2.389828628283801</v>
+        <v>2.402019694541912</v>
       </c>
       <c r="D61">
-        <v>4.608900000000001</v>
+        <v>4.5869</v>
       </c>
       <c r="E61">
-        <v>11.01448116489721</v>
+        <v>11.0178241368943</v>
       </c>
       <c r="F61">
         <v>65</v>
@@ -2322,13 +2335,13 @@
         <v>85</v>
       </c>
       <c r="C62">
-        <v>3.052716971060664</v>
+        <v>3.148642850221658</v>
       </c>
       <c r="D62">
-        <v>4.902</v>
+        <v>4.912</v>
       </c>
       <c r="E62">
-        <v>14.96441859213938</v>
+        <v>15.46613368028878</v>
       </c>
       <c r="F62">
         <v>111</v>
@@ -2338,6 +2351,60 @@
       </c>
       <c r="H62">
         <v>3.108707193977267</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>65</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>111</v>
+      </c>
+      <c r="B3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>222</v>
+      </c>
+      <c r="B4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/submission/q4_base_location.xlsx
+++ b/outputs/submission/q4_base_location.xlsx
@@ -768,7 +768,7 @@
         <v>25.9600841186291</v>
       </c>
       <c r="D7" t="n">
-        <v>5.002000000000001</v>
+        <v>5.002</v>
       </c>
       <c r="E7" t="n">
         <v>129.8523407613828</v>
@@ -1128,10 +1128,10 @@
         <v>0.8373578803924049</v>
       </c>
       <c r="D19" t="n">
-        <v>3.567710440003781</v>
+        <v>3.56771044000378</v>
       </c>
       <c r="E19" t="n">
-        <v>2.98745045189542</v>
+        <v>2.987450451895419</v>
       </c>
       <c r="F19" t="n">
         <v>33</v>
@@ -1368,10 +1368,10 @@
         <v>5.363602807817085</v>
       </c>
       <c r="D27" t="n">
-        <v>6.527000000000005</v>
+        <v>6.527000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>35.00823552662214</v>
+        <v>35.00823552662212</v>
       </c>
       <c r="F27" t="n">
         <v>111</v>
@@ -2148,10 +2148,10 @@
         <v>2.4260424794793</v>
       </c>
       <c r="D53" t="n">
-        <v>3.701500000000001</v>
+        <v>3.7015</v>
       </c>
       <c r="E53" t="n">
-        <v>8.979996237792632</v>
+        <v>8.979996237792628</v>
       </c>
       <c r="F53" t="n">
         <v>111</v>
@@ -2208,7 +2208,7 @@
         <v>2.751724916137945</v>
       </c>
       <c r="D55" t="n">
-        <v>8.204499999999999</v>
+        <v>8.204500000000001</v>
       </c>
       <c r="E55" t="n">
         <v>22.57652707445377</v>
@@ -2268,10 +2268,10 @@
         <v>7.65442465999378</v>
       </c>
       <c r="D57" t="n">
-        <v>9.283000000000005</v>
+        <v>9.282999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>71.05602411872229</v>
+        <v>71.05602411872226</v>
       </c>
       <c r="F57" t="n">
         <v>111</v>
@@ -2358,7 +2358,7 @@
         <v>3.744159174953809</v>
       </c>
       <c r="D60" t="n">
-        <v>8.229416666666669</v>
+        <v>8.229416666666667</v>
       </c>
       <c r="E60" t="n">
         <v>30.8122459170178</v>
